--- a/examples/example_specimens.xlsx
+++ b/examples/example_specimens.xlsx
@@ -895,7 +895,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>alpine meadow</t>
+          <t>rocky slope beside alpine woodland</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
